--- a/athlete_forms/015_half_marathon_training_mileage_tracker--athlete_forms.xlsx
+++ b/athlete_forms/015_half_marathon_training_mileage_tracker--athlete_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1160,17 +1160,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mileage_unit_choices</t>
+          <t>pace_unit_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kilometers</t>
+          <t>minutes_per_mile</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kilometers</t>
+          <t>Minutes per Mile</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>minutes_per_mile</t>
+          <t>minutes_per_kilometer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minutes per Mile</t>
+          <t>Minutes per Kilometer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pace_unit_choices</t>
+          <t>goal_unit_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>minutes_per_kilometer</t>
+          <t>miles</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minutes per Kilometer</t>
+          <t>Miles</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>miles</t>
+          <t>kilometers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Kilometers</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kilometers</t>
+          <t>kms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kilometers</t>
+          <t>Kms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>goal_unit_choices</t>
+          <t>goal_pace_unit_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kms</t>
+          <t>minutes_per_mile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kms</t>
+          <t>Minutes per Mile</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>minutes_per_mile</t>
+          <t>minutes_per_kilometer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minutes per Mile</t>
+          <t>Minutes per Kilometer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>goal_pace_unit_choices</t>
+          <t>training_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>minutes_per_kilometer</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minutes per Kilometer</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>training_phase_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>end_of_base_building</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>End of Base Building</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>end_of_base_building</t>
+          <t>end_of_building</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>End of Base Building</t>
+          <t>End of Building</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>end_of_building</t>
+          <t>base_building</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>End of Building</t>
+          <t>Base Building</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>base_building</t>
+          <t>base_building_endurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Base Building</t>
+          <t>Base Building Endurance</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>base_building_endurance</t>
+          <t>base_building_intensity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Base Building Endurance</t>
+          <t>Base Building Intensity</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>training_phase_choices</t>
+          <t>workout_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>base_building_intensity</t>
+          <t>running</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Base Building Intensity</t>
+          <t>Running</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>strength_and_conditioning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Running</t>
+          <t>Strength and Conditioning</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>strength_and_conditioning</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Strength and Conditioning</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>rest_and_recovery</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Endurance</t>
+          <t>Rest and Recovery</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>workout_type_choices</t>
+          <t>workout_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rest_and_recovery</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rest and Recovery</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bi-weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>workout_frequency_choices</t>
+          <t>workout_duration_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>under_30_minutes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Under 30 minutes</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>under_30_minutes</t>
+          <t>30-60_minutes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Under 30 minutes</t>
+          <t>30-60 minutes</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30-60_minutes</t>
+          <t>60-90_minutes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>30-60 minutes</t>
+          <t>60-90 minutes</t>
         </is>
       </c>
     </row>
@@ -1624,27 +1624,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>60-90_minutes</t>
+          <t>more_than_90_minutes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>60-90 minutes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>workout_duration_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>more_than_90_minutes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>More than 90 minutes</t>
         </is>
